--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
